--- a/AdventureWorks_Analysis.xlsx
+++ b/AdventureWorks_Analysis.xlsx
@@ -9666,7 +9666,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9715,7 +9715,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9764,7 +9764,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9856,7 +9856,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9905,7 +9905,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9954,7 +9954,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0800-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10003,7 +10003,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0900-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
